--- a/src/sim_results/soft.xlsx
+++ b/src/sim_results/soft.xlsx
@@ -38,17 +38,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="000000FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,15 +70,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -497,52 +500,52 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>unknown</t>
         </is>
       </c>
     </row>
@@ -550,54 +553,54 @@
       <c r="A3" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>unknown</t>
         </is>
       </c>
     </row>
@@ -605,54 +608,54 @@
       <c r="A4" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>unknown</t>
         </is>
       </c>
     </row>
@@ -660,54 +663,54 @@
       <c r="A5" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>stand</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>stand</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>unknown</t>
         </is>
       </c>
     </row>
@@ -717,52 +720,52 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>hit</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>hit</t>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
         </is>
       </c>
     </row>
@@ -770,52 +773,52 @@
       <c r="A7" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>hit</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
+          <t>double</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
@@ -827,52 +830,52 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>hit</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>double</t>
         </is>
       </c>
     </row>
@@ -880,54 +883,54 @@
       <c r="A9" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>hit</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>double</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
+          <t>double</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
     </row>
@@ -935,52 +938,52 @@
       <c r="A10" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>stand</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>stand</t>
         </is>
